--- a/Collections/EURO/Finland/#EURO#Finland#Commemorative#[2004-present]#UNC.xlsx
+++ b/Collections/EURO/Finland/#EURO#Finland#Commemorative#[2004-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Finland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA565F3-3C5F-41EF-9E6E-B6082FBC9928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03FB05F-2CF9-43F8-B5BF-D5C6D61100A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1430" windowWidth="33150" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -701,6 +701,9 @@
     <xf numFmtId="3" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,23 +731,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="23">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -753,15 +754,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -936,9 +928,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1220,28 +1212,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23"/>
-      <c r="C1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="33" t="s">
+      <c r="C1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="31" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="32"/>
+      <c r="J1" s="33"/>
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="23" t="s">
         <v>71</v>
       </c>
@@ -1260,7 +1252,7 @@
       <c r="G2" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="26" t="s">
         <v>87</v>
       </c>
       <c r="I2" s="19" t="s">
@@ -1301,7 +1293,7 @@
         <v>88</v>
       </c>
       <c r="K3" s="8" t="str">
-        <f t="shared" ref="K3" si="0">IF(OR(AND(I3&gt;1,I3&lt;&gt;"-")),"Can exchange","")</f>
+        <f>IF(OR(AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1335,7 +1327,7 @@
         <v>88</v>
       </c>
       <c r="K4" s="8" t="str">
-        <f t="shared" ref="K4:K5" si="1">IF(OR(AND(I4&gt;1,I4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="K4:K41" si="0">IF(OR(AND(I4&gt;1,I4&lt;&gt;"-"),AND(J4&gt;1,J4&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1369,7 +1361,7 @@
         <v>88</v>
       </c>
       <c r="K5" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1403,7 +1395,7 @@
         <v>88</v>
       </c>
       <c r="K6" s="8" t="str">
-        <f t="shared" ref="K6:K28" si="2">IF(OR(AND(I6&gt;1,I6&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1439,7 +1431,7 @@
         <v>88</v>
       </c>
       <c r="K7" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1473,7 +1465,7 @@
         <v>88</v>
       </c>
       <c r="K8" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1507,7 +1499,7 @@
         <v>88</v>
       </c>
       <c r="K9" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1543,7 +1535,7 @@
         <v>88</v>
       </c>
       <c r="K10" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1577,7 +1569,7 @@
         <v>88</v>
       </c>
       <c r="K11" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1611,7 +1603,7 @@
         <v>88</v>
       </c>
       <c r="K12" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1645,7 +1637,7 @@
         <v>88</v>
       </c>
       <c r="K13" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1681,7 +1673,7 @@
         <v>88</v>
       </c>
       <c r="K14" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1715,7 +1707,7 @@
         <v>88</v>
       </c>
       <c r="K15" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="U15" s="22"/>
@@ -1751,7 +1743,7 @@
         <v>88</v>
       </c>
       <c r="K16" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1785,7 +1777,7 @@
         <v>88</v>
       </c>
       <c r="K17" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1819,7 +1811,7 @@
         <v>88</v>
       </c>
       <c r="K18" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1853,7 +1845,7 @@
         <v>88</v>
       </c>
       <c r="K19" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1887,7 +1879,7 @@
         <v>88</v>
       </c>
       <c r="K20" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1923,7 +1915,7 @@
         <v>88</v>
       </c>
       <c r="K21" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1957,7 +1949,7 @@
         <v>88</v>
       </c>
       <c r="K22" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -1991,7 +1983,7 @@
         <v>88</v>
       </c>
       <c r="K23" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="T23" s="22"/>
@@ -2027,7 +2019,7 @@
         <v>88</v>
       </c>
       <c r="K24" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2061,7 +2053,7 @@
         <v>88</v>
       </c>
       <c r="K25" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2095,7 +2087,7 @@
         <v>88</v>
       </c>
       <c r="K26" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2129,7 +2121,7 @@
         <v>88</v>
       </c>
       <c r="K27" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2163,7 +2155,7 @@
         <v>88</v>
       </c>
       <c r="K28" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2197,7 +2189,7 @@
         <v>88</v>
       </c>
       <c r="K29" s="8" t="str">
-        <f t="shared" ref="K29:K30" si="3">IF(OR(AND(I29&gt;1,I29&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2231,7 +2223,7 @@
         <v>88</v>
       </c>
       <c r="K30" s="8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2265,7 +2257,7 @@
         <v>88</v>
       </c>
       <c r="K31" s="8" t="str">
-        <f t="shared" ref="K31:K32" si="4">IF(OR(AND(I31&gt;1,I31&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="U31" s="22"/>
@@ -2301,7 +2293,7 @@
         <v>88</v>
       </c>
       <c r="K32" s="8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2335,7 +2327,7 @@
         <v>88</v>
       </c>
       <c r="K33" s="8" t="str">
-        <f t="shared" ref="K33:K37" si="5">IF(OR(AND(I33&gt;1,I33&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2371,7 +2363,7 @@
         <v>88</v>
       </c>
       <c r="K34" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2405,7 +2397,7 @@
         <v>88</v>
       </c>
       <c r="K35" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2439,7 +2431,7 @@
         <v>88</v>
       </c>
       <c r="K36" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2473,7 +2465,7 @@
         <v>88</v>
       </c>
       <c r="K37" s="8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -2506,6 +2498,10 @@
       <c r="J38" s="24" t="s">
         <v>88</v>
       </c>
+      <c r="K38" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
@@ -2536,6 +2532,10 @@
       <c r="J39" s="24" t="s">
         <v>88</v>
       </c>
+      <c r="K39" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="40" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
@@ -2566,6 +2566,10 @@
       <c r="J40" s="7">
         <v>1</v>
       </c>
+      <c r="K40" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="U40" s="22"/>
       <c r="V40" s="22"/>
     </row>
@@ -2597,6 +2601,10 @@
       </c>
       <c r="J41" s="7">
         <v>1</v>
+      </c>
+      <c r="K41" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2608,7 +2616,7 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="I3 I5 I7 I9 I11 I13 I15 I17 I19 I21 I23 I25">
-    <cfRule type="containsText" dxfId="23" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2625,7 +2633,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I6 I8 I10 I12 I14 I16 I18 I20 I22 I24 I26">
-    <cfRule type="containsText" dxfId="22" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2642,7 +2650,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27">
-    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2659,7 +2667,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="containsText" dxfId="20" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2676,7 +2684,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="19" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2693,7 +2701,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="containsText" dxfId="18" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2710,7 +2718,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="17" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2727,7 +2735,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="16" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2744,7 +2752,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="15" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2761,7 +2769,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37">
-    <cfRule type="containsText" dxfId="14" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2778,7 +2786,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="containsText" dxfId="13" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2795,7 +2803,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I35">
-    <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2812,7 +2820,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36">
-    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2829,7 +2837,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2846,7 +2854,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I39">
-    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2926,12 +2934,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J41))))</formula>
     </cfRule>
   </conditionalFormatting>
